--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_arica_y_parinacota.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:44</t>
+    <t xml:space="preserve">2026-09-24 00:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -519,10 +519,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3">
@@ -536,7 +536,7 @@
         <v>-0.31</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4">
@@ -547,10 +547,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5">
@@ -564,7 +564,7 @@
         <v>0.22</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         <v>0.32</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7">
@@ -589,10 +589,10 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8">
@@ -603,10 +603,10 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -617,10 +617,10 @@
         <v>11</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10">
@@ -631,10 +631,10 @@
         <v>11</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11">
@@ -645,10 +645,10 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12">
@@ -659,10 +659,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13">
@@ -673,10 +673,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14">
@@ -687,10 +687,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15">
@@ -701,10 +701,10 @@
         <v>11</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16">
@@ -718,7 +718,7 @@
         <v>0.15</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="17">
@@ -729,10 +729,10 @@
         <v>11</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18">
@@ -746,7 +746,7 @@
         <v>-0.41</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_arica_y_parinacota.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:35</t>
+    <t xml:space="preserve">2026-10-01 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_arica_y_parinacota.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:06</t>
+    <t xml:space="preserve">2026-10-05 19:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
